--- a/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>The clinical reason why the AI was used for this specific patient.</t>
+    <t>Records the clinical indication or case-specific reason for applying the AI system in the documented patient context.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -335,7 +335,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/eu-case-specific-indication-vs</t>
+    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/eu-ai-case-specific-indication-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ext-1
@@ -673,7 +673,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.51953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>79</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Observation</t>
+    <t>element:Provenance</t>
   </si>
   <si>
     <t>ID</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-case-specific-indication.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/StructureDefinition/case-specific-indication</t>
+    <t>http://example.org/fhir/trust-ai-transparency/StructureDefinition/case-specific-indication</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:39:53+00:00</t>
+    <t>2026-09-09T11:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -335,7 +335,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/eu-ai-case-specific-indication-vs</t>
+    <t>http://example.org/fhir/trust-ai-transparency/ValueSet/trust-ai-case-specific-indication-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ext-1
@@ -673,7 +673,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.9453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
